--- a/xlsx/Power/p11.xlsx
+++ b/xlsx/Power/p11.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1082D0B0-0A2B-47C4-9A12-FE736D0B9B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF49BB44-369D-4206-A320-77479B5031D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{C3A456FA-7B98-4B1E-AE32-7B64A12CA6F4}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{C3A456FA-7B98-4B1E-AE32-7B64A12CA6F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,10 +404,10 @@
         <v>0.93400000000000005</v>
       </c>
       <c r="C1">
-        <v>0.99199999999999999</v>
+        <v>0.83499999999999996</v>
       </c>
       <c r="D1">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="E1">
         <v>1</v>
@@ -436,10 +436,10 @@
         <v>0.91600000000000004</v>
       </c>
       <c r="C2">
-        <v>0.98599999999999999</v>
+        <v>0.82399999999999995</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -468,7 +468,7 @@
         <v>0.90700000000000003</v>
       </c>
       <c r="C3">
-        <v>0.98299999999999998</v>
+        <v>0.98799999999999999</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -494,13 +494,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.55000000000000004</v>
+        <v>0.58099999999999996</v>
       </c>
       <c r="B4">
-        <v>0.88600000000000001</v>
+        <v>0.89200000000000002</v>
       </c>
       <c r="C4">
-        <v>0.97099999999999997</v>
+        <v>0.97199999999999998</v>
       </c>
       <c r="D4">
         <v>0.998</v>
@@ -564,10 +564,10 @@
         <v>0.81899999999999995</v>
       </c>
       <c r="C6">
-        <v>0.94899999999999995</v>
+        <v>0.99</v>
       </c>
       <c r="D6">
-        <v>0.98899999999999999</v>
+        <v>0.997</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -596,7 +596,7 @@
         <v>0.78400000000000003</v>
       </c>
       <c r="C7">
-        <v>0.93</v>
+        <v>0.92900000000000005</v>
       </c>
       <c r="D7">
         <v>0.97899999999999998</v>
@@ -628,19 +628,19 @@
         <v>0.88</v>
       </c>
       <c r="C8">
-        <v>0.97799999999999998</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="D8">
+        <v>0.95099999999999996</v>
+      </c>
+      <c r="E8">
+        <v>0.995</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
         <v>0.999</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -660,28 +660,28 @@
         <v>0.63500000000000001</v>
       </c>
       <c r="C9">
-        <v>0.59299999999999997</v>
+        <v>0.88800000000000001</v>
       </c>
       <c r="D9">
-        <v>0.41899999999999998</v>
+        <v>0.997</v>
       </c>
       <c r="E9">
-        <v>0.443</v>
+        <v>0.96199999999999997</v>
       </c>
       <c r="F9">
-        <v>0.59799999999999998</v>
+        <v>0.77</v>
       </c>
       <c r="G9">
-        <v>0.64600000000000002</v>
+        <v>0.745</v>
       </c>
       <c r="H9">
-        <v>0.74</v>
+        <v>0.78300000000000003</v>
       </c>
       <c r="I9">
-        <v>0.81299999999999994</v>
+        <v>0.84299999999999997</v>
       </c>
       <c r="J9">
-        <v>0.9</v>
+        <v>0.91600000000000004</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p11.xlsx
+++ b/xlsx/Power/p11.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF49BB44-369D-4206-A320-77479B5031D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68BCDEC1-CAC5-46E2-8BE7-904755BB8A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{C3A456FA-7B98-4B1E-AE32-7B64A12CA6F4}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{C3A456FA-7B98-4B1E-AE32-7B64A12CA6F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,10 +404,10 @@
         <v>0.93400000000000005</v>
       </c>
       <c r="C1">
-        <v>0.83499999999999996</v>
+        <v>0.99199999999999999</v>
       </c>
       <c r="D1">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="E1">
         <v>1</v>
@@ -430,16 +430,16 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0.58499999999999996</v>
+        <v>0.58599999999999997</v>
       </c>
       <c r="B2">
         <v>0.91600000000000004</v>
       </c>
       <c r="C2">
-        <v>0.82399999999999995</v>
+        <v>0.98599999999999999</v>
       </c>
       <c r="D2">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -468,7 +468,7 @@
         <v>0.90700000000000003</v>
       </c>
       <c r="C3">
-        <v>0.98799999999999999</v>
+        <v>0.98299999999999998</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -494,13 +494,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.58099999999999996</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="B4">
-        <v>0.89200000000000002</v>
+        <v>0.88600000000000001</v>
       </c>
       <c r="C4">
-        <v>0.97199999999999998</v>
+        <v>0.97099999999999997</v>
       </c>
       <c r="D4">
         <v>0.998</v>
@@ -558,16 +558,16 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0.497</v>
+        <v>0.498</v>
       </c>
       <c r="B6">
         <v>0.81899999999999995</v>
       </c>
       <c r="C6">
-        <v>0.99</v>
+        <v>0.94899999999999995</v>
       </c>
       <c r="D6">
-        <v>0.997</v>
+        <v>0.98899999999999999</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -596,7 +596,7 @@
         <v>0.78400000000000003</v>
       </c>
       <c r="C7">
-        <v>0.92900000000000005</v>
+        <v>0.93</v>
       </c>
       <c r="D7">
         <v>0.97899999999999998</v>
@@ -622,25 +622,25 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>0.43</v>
+        <v>0.43099999999999999</v>
       </c>
       <c r="B8">
         <v>0.88</v>
       </c>
       <c r="C8">
-        <v>0.32500000000000001</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="D8">
-        <v>0.95099999999999996</v>
+        <v>0.999</v>
       </c>
       <c r="E8">
-        <v>0.995</v>
+        <v>1</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8">
-        <v>0.999</v>
+        <v>1</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -660,28 +660,28 @@
         <v>0.63500000000000001</v>
       </c>
       <c r="C9">
-        <v>0.88800000000000001</v>
+        <v>0.59299999999999997</v>
       </c>
       <c r="D9">
-        <v>0.997</v>
+        <v>0.41899999999999998</v>
       </c>
       <c r="E9">
-        <v>0.96199999999999997</v>
+        <v>0.443</v>
       </c>
       <c r="F9">
-        <v>0.77</v>
+        <v>0.59799999999999998</v>
       </c>
       <c r="G9">
-        <v>0.745</v>
+        <v>0.64600000000000002</v>
       </c>
       <c r="H9">
-        <v>0.78300000000000003</v>
+        <v>0.74</v>
       </c>
       <c r="I9">
-        <v>0.84299999999999997</v>
+        <v>0.81299999999999994</v>
       </c>
       <c r="J9">
-        <v>0.91600000000000004</v>
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p11.xlsx
+++ b/xlsx/Power/p11.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68BCDEC1-CAC5-46E2-8BE7-904755BB8A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2527D4D2-1329-48DF-AC4E-759A7E25BC88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{C3A456FA-7B98-4B1E-AE32-7B64A12CA6F4}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{C3A456FA-7B98-4B1E-AE32-7B64A12CA6F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -398,10 +398,10 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>0.60899999999999999</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="B1">
-        <v>0.93400000000000005</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="C1">
         <v>0.99199999999999999</v>
@@ -430,10 +430,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0.58599999999999997</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="B2">
-        <v>0.91600000000000004</v>
+        <v>0.91700000000000004</v>
       </c>
       <c r="C2">
         <v>0.98599999999999999</v>
@@ -462,10 +462,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>0.57199999999999995</v>
+        <v>0.56899999999999995</v>
       </c>
       <c r="B3">
-        <v>0.90700000000000003</v>
+        <v>0.90800000000000003</v>
       </c>
       <c r="C3">
         <v>0.98299999999999998</v>
@@ -494,13 +494,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.55000000000000004</v>
+        <v>0.54900000000000004</v>
       </c>
       <c r="B4">
-        <v>0.88600000000000001</v>
+        <v>0.88800000000000001</v>
       </c>
       <c r="C4">
-        <v>0.97099999999999997</v>
+        <v>0.97199999999999998</v>
       </c>
       <c r="D4">
         <v>0.998</v>
@@ -526,42 +526,42 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>1</v>
+        <v>3.1E-2</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0.17</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0.42199999999999999</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0.64600000000000002</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0.79400000000000004</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0.90800000000000003</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0.95699999999999996</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0.97199999999999998</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0.98899999999999999</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0.998</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0.498</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="B6">
-        <v>0.81899999999999995</v>
+        <v>0.81799999999999995</v>
       </c>
       <c r="C6">
         <v>0.94899999999999995</v>
@@ -590,7 +590,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>0.45300000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="B7">
         <v>0.78400000000000003</v>
@@ -599,7 +599,7 @@
         <v>0.93</v>
       </c>
       <c r="D7">
-        <v>0.97899999999999998</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="E7">
         <v>0.997</v>
@@ -657,31 +657,31 @@
         <v>0.36099999999999999</v>
       </c>
       <c r="B9">
-        <v>0.63500000000000001</v>
+        <v>0.63800000000000001</v>
       </c>
       <c r="C9">
         <v>0.59299999999999997</v>
       </c>
       <c r="D9">
-        <v>0.41899999999999998</v>
+        <v>0.42099999999999999</v>
       </c>
       <c r="E9">
-        <v>0.443</v>
+        <v>0.439</v>
       </c>
       <c r="F9">
-        <v>0.59799999999999998</v>
+        <v>0.59899999999999998</v>
       </c>
       <c r="G9">
-        <v>0.64600000000000002</v>
+        <v>0.64200000000000002</v>
       </c>
       <c r="H9">
-        <v>0.74</v>
+        <v>0.74199999999999999</v>
       </c>
       <c r="I9">
-        <v>0.81299999999999994</v>
+        <v>0.81699999999999995</v>
       </c>
       <c r="J9">
-        <v>0.9</v>
+        <v>0.90300000000000002</v>
       </c>
     </row>
   </sheetData>
